--- a/AAII_Financials/Yearly/BKV_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BKV_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="92">
   <si>
     <t>BKV</t>
   </si>
@@ -715,13 +715,13 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>893800</v>
+        <v>1140800</v>
       </c>
       <c r="E8" s="3">
-        <v>590500</v>
+        <v>805700</v>
       </c>
       <c r="F8" s="3">
-        <v>738600</v>
+        <v>1009600</v>
       </c>
       <c r="G8" s="3">
         <v>1660200</v>
@@ -748,13 +748,13 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>403700</v>
+        <v>776500</v>
       </c>
       <c r="E9" s="3">
-        <v>359400</v>
+        <v>667400</v>
       </c>
       <c r="F9" s="3">
-        <v>399600</v>
+        <v>578000</v>
       </c>
       <c r="G9" s="3">
         <v>340300</v>
@@ -781,13 +781,13 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>490100</v>
+        <v>364300</v>
       </c>
       <c r="E10" s="3">
-        <v>231100</v>
+        <v>138300</v>
       </c>
       <c r="F10" s="3">
-        <v>338900</v>
+        <v>431600</v>
       </c>
       <c r="G10" s="3">
         <v>1320000</v>
@@ -895,7 +895,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>27000</v>
+        <v>8300</v>
       </c>
       <c r="E14" s="3">
         <v>-6400</v>
@@ -928,13 +928,13 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>157500</v>
+        <v>195700</v>
       </c>
       <c r="E15" s="3">
-        <v>217500</v>
+        <v>255500</v>
       </c>
       <c r="F15" s="3">
-        <v>223400</v>
+        <v>255100</v>
       </c>
       <c r="G15" s="3">
         <v>118900</v>
@@ -973,13 +973,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>649100</v>
+        <v>828800</v>
       </c>
       <c r="E17" s="3">
-        <v>755900</v>
+        <v>880500</v>
       </c>
       <c r="F17" s="3">
-        <v>583200</v>
+        <v>770700</v>
       </c>
       <c r="G17" s="3">
         <v>1337400</v>
@@ -1006,13 +1006,13 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>244700</v>
+        <v>312000</v>
       </c>
       <c r="E18" s="3">
-        <v>-165400</v>
+        <v>-74800</v>
       </c>
       <c r="F18" s="3">
-        <v>155400</v>
+        <v>238900</v>
       </c>
       <c r="G18" s="3">
         <v>322900</v>
@@ -1054,13 +1054,13 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-19700</v>
+        <v>-9300</v>
       </c>
       <c r="E20" s="3">
-        <v>-19400</v>
+        <v>-9000</v>
       </c>
       <c r="F20" s="3">
-        <v>-23000</v>
+        <v>-5400</v>
       </c>
       <c r="G20" s="3">
         <v>-9900</v>
@@ -1087,13 +1087,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>421900</v>
+        <v>517100</v>
       </c>
       <c r="E21" s="3">
-        <v>71600</v>
+        <v>189700</v>
       </c>
       <c r="F21" s="3">
-        <v>401800</v>
+        <v>499500</v>
       </c>
       <c r="G21" s="3">
         <v>451700</v>
@@ -1120,13 +1120,13 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>28600</v>
+        <v>92000</v>
       </c>
       <c r="E22" s="3">
-        <v>50800</v>
+        <v>123700</v>
       </c>
       <c r="F22" s="3">
-        <v>77000</v>
+        <v>127500</v>
       </c>
       <c r="G22" s="3">
         <v>37200</v>
@@ -1153,13 +1153,13 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>210300</v>
+        <v>225200</v>
       </c>
       <c r="E23" s="3">
-        <v>-186500</v>
+        <v>-175800</v>
       </c>
       <c r="F23" s="3">
-        <v>145100</v>
+        <v>162100</v>
       </c>
       <c r="G23" s="3">
         <v>472800</v>
@@ -1186,13 +1186,13 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>35400</v>
+        <v>36900</v>
       </c>
       <c r="E24" s="3">
-        <v>-43600</v>
+        <v>-42400</v>
       </c>
       <c r="F24" s="3">
-        <v>28200</v>
+        <v>30100</v>
       </c>
       <c r="G24" s="3">
         <v>62700</v>
@@ -1252,13 +1252,13 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>174800</v>
+        <v>188300</v>
       </c>
       <c r="E26" s="3">
-        <v>-142900</v>
+        <v>-133400</v>
       </c>
       <c r="F26" s="3">
-        <v>116900</v>
+        <v>132000</v>
       </c>
       <c r="G26" s="3">
         <v>410100</v>
@@ -1285,13 +1285,13 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>171700</v>
+        <v>177700</v>
       </c>
       <c r="E27" s="3">
-        <v>-142900</v>
+        <v>-138700</v>
       </c>
       <c r="F27" s="3">
-        <v>116900</v>
+        <v>123600</v>
       </c>
       <c r="G27" s="3">
         <v>410100</v>
@@ -1450,13 +1450,13 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>19700</v>
+        <v>9300</v>
       </c>
       <c r="E32" s="3">
-        <v>19400</v>
+        <v>9000</v>
       </c>
       <c r="F32" s="3">
-        <v>23000</v>
+        <v>5400</v>
       </c>
       <c r="G32" s="3">
         <v>9900</v>
@@ -1483,13 +1483,13 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>173100</v>
+        <v>179200</v>
       </c>
       <c r="E33" s="3">
-        <v>-142900</v>
+        <v>-138700</v>
       </c>
       <c r="F33" s="3">
-        <v>116900</v>
+        <v>123600</v>
       </c>
       <c r="G33" s="3">
         <v>410100</v>
@@ -1549,13 +1549,13 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>173100</v>
+        <v>179200</v>
       </c>
       <c r="E35" s="3">
-        <v>-142900</v>
+        <v>-138700</v>
       </c>
       <c r="F35" s="3">
-        <v>116900</v>
+        <v>123600</v>
       </c>
       <c r="G35" s="3">
         <v>410100</v>
@@ -1650,10 +1650,10 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>199400</v>
+        <v>248400</v>
       </c>
       <c r="E41" s="3">
-        <v>14900</v>
+        <v>81200</v>
       </c>
       <c r="F41" s="3">
         <v>25400</v>
@@ -1716,10 +1716,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>112000</v>
+        <v>128900</v>
       </c>
       <c r="E43" s="3">
-        <v>65800</v>
+        <v>77900</v>
       </c>
       <c r="F43" s="3">
         <v>49100</v>
@@ -1749,10 +1749,10 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>6100</v>
+        <v>20000</v>
       </c>
       <c r="E44" s="3">
-        <v>6300</v>
+        <v>20100</v>
       </c>
       <c r="F44" s="3">
         <v>9900</v>
@@ -1782,10 +1782,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>64000</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
+        <v>83400</v>
+      </c>
+      <c r="E45" s="3">
+        <v>24300</v>
       </c>
       <c r="F45" s="3">
         <v>84300</v>
@@ -1815,10 +1815,10 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>387900</v>
+        <v>511400</v>
       </c>
       <c r="E46" s="3">
-        <v>94600</v>
+        <v>235000</v>
       </c>
       <c r="F46" s="3">
         <v>312200</v>
@@ -1847,11 +1847,11 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>130100</v>
-      </c>
-      <c r="E47" s="3">
-        <v>115200</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F47" s="3">
         <v>104800</v>
@@ -1881,10 +1881,10 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2545100</v>
+        <v>3351700</v>
       </c>
       <c r="E48" s="3">
-        <v>1985600</v>
+        <v>2825100</v>
       </c>
       <c r="F48" s="3">
         <v>2209400</v>
@@ -2013,10 +2013,10 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>48300</v>
+        <v>57700</v>
       </c>
       <c r="E52" s="3">
-        <v>17300</v>
+        <v>20300</v>
       </c>
       <c r="F52" s="3">
         <v>38400</v>
@@ -2079,10 +2079,10 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>3129700</v>
+        <v>3939300</v>
       </c>
       <c r="E54" s="3">
-        <v>2231100</v>
+        <v>3098800</v>
       </c>
       <c r="F54" s="3">
         <v>2683100</v>
@@ -2142,10 +2142,10 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>84400</v>
+        <v>100400</v>
       </c>
       <c r="E57" s="3">
-        <v>53200</v>
+        <v>75200</v>
       </c>
       <c r="F57" s="3">
         <v>47500</v>
@@ -2175,10 +2175,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>7700</v>
+        <v>208100</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>9400</v>
       </c>
       <c r="F58" s="3">
         <v>239400</v>
@@ -2208,10 +2208,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>28000</v>
+        <v>151800</v>
       </c>
       <c r="E59" s="3">
-        <v>48700</v>
+        <v>68700</v>
       </c>
       <c r="F59" s="3">
         <v>23700</v>
@@ -2241,10 +2241,10 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>217900</v>
+        <v>564600</v>
       </c>
       <c r="E60" s="3">
-        <v>166200</v>
+        <v>236700</v>
       </c>
       <c r="F60" s="3">
         <v>412300</v>
@@ -2274,10 +2274,10 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>492000</v>
+        <v>942900</v>
       </c>
       <c r="E61" s="3">
-        <v>165000</v>
+        <v>849800</v>
       </c>
       <c r="F61" s="3">
         <v>414700</v>
@@ -2307,10 +2307,10 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>249100</v>
+        <v>236100</v>
       </c>
       <c r="E62" s="3">
-        <v>251600</v>
+        <v>367000</v>
       </c>
       <c r="F62" s="3">
         <v>421500</v>
@@ -2439,10 +2439,10 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1082300</v>
+        <v>1872500</v>
       </c>
       <c r="E66" s="3">
-        <v>671500</v>
+        <v>1546300</v>
       </c>
       <c r="F66" s="3">
         <v>1392400</v>
@@ -2619,10 +2619,10 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>288800</v>
+        <v>309100</v>
       </c>
       <c r="E72" s="3">
-        <v>117100</v>
+        <v>131300</v>
       </c>
       <c r="F72" s="3">
         <v>259900</v>
@@ -2751,10 +2751,10 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2038700</v>
+        <v>1985800</v>
       </c>
       <c r="E76" s="3">
-        <v>1559600</v>
+        <v>1500700</v>
       </c>
       <c r="F76" s="3">
         <v>1290800</v>
@@ -2855,13 +2855,13 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>173100</v>
+        <v>179200</v>
       </c>
       <c r="E81" s="3">
-        <v>-142900</v>
+        <v>-138700</v>
       </c>
       <c r="F81" s="3">
-        <v>116900</v>
+        <v>123600</v>
       </c>
       <c r="G81" s="3">
         <v>410100</v>
@@ -2903,13 +2903,13 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>143900</v>
+        <v>182200</v>
       </c>
       <c r="E83" s="3">
-        <v>203800</v>
+        <v>241800</v>
       </c>
       <c r="F83" s="3">
-        <v>211200</v>
+        <v>243000</v>
       </c>
       <c r="G83" s="3">
         <v>117200</v>
@@ -3101,13 +3101,13 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>242700</v>
+        <v>280400</v>
       </c>
       <c r="E89" s="3">
-        <v>118500</v>
+        <v>115400</v>
       </c>
       <c r="F89" s="3">
-        <v>123100</v>
+        <v>260300</v>
       </c>
       <c r="G89" s="3">
         <v>349200</v>
@@ -3149,13 +3149,13 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-572300</v>
+        <v>-577200</v>
       </c>
       <c r="E91" s="3">
-        <v>-100900</v>
+        <v>-105400</v>
       </c>
       <c r="F91" s="3">
-        <v>-192600</v>
+        <v>-681800</v>
       </c>
       <c r="G91" s="3">
         <v>-248100</v>
@@ -3248,13 +3248,13 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-564900</v>
+        <v>-576400</v>
       </c>
       <c r="E94" s="3">
-        <v>36100</v>
+        <v>34300</v>
       </c>
       <c r="F94" s="3">
-        <v>-177800</v>
+        <v>-663100</v>
       </c>
       <c r="G94" s="3">
         <v>-865600</v>
@@ -3428,13 +3428,13 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>506700</v>
+        <v>463300</v>
       </c>
       <c r="E100" s="3">
-        <v>-304800</v>
+        <v>-314800</v>
       </c>
       <c r="F100" s="3">
-        <v>66700</v>
+        <v>498500</v>
       </c>
       <c r="G100" s="3">
         <v>534800</v>
@@ -3494,13 +3494,13 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>184500</v>
+        <v>167300</v>
       </c>
       <c r="E102" s="3">
-        <v>-150200</v>
+        <v>-165100</v>
       </c>
       <c r="F102" s="3">
-        <v>11900</v>
+        <v>95600</v>
       </c>
       <c r="G102" s="3">
         <v>18500</v>
